--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/pre LAM_HRM-2031-0480/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/pre LAM_HRM-2031-0480/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.45174</v>
+        <v>17.49486</v>
       </c>
       <c r="D2" t="n">
-        <v>16.76326</v>
+        <v>17.07025</v>
       </c>
       <c r="E2" t="n">
-        <v>17.01319</v>
+        <v>17.33258</v>
       </c>
       <c r="F2" t="n">
-        <v>43.75985</v>
+        <v>43.74413</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05194</v>
+        <v>0.05303</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82857</v>
+        <v>1.86669</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.33861</v>
+        <v>17.37899</v>
       </c>
       <c r="D3" t="n">
-        <v>17.10657</v>
+        <v>17.1211</v>
       </c>
       <c r="E3" t="n">
-        <v>17.18623</v>
+        <v>17.32425</v>
       </c>
       <c r="F3" t="n">
-        <v>43.91521</v>
+        <v>44.57797</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05153</v>
+        <v>0.05278</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82393</v>
+        <v>1.84646</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.14239</v>
+        <v>17.9033</v>
       </c>
       <c r="D4" t="n">
-        <v>17.04176</v>
+        <v>17.12833</v>
       </c>
       <c r="E4" t="n">
-        <v>17.32737</v>
+        <v>17.55143</v>
       </c>
       <c r="F4" t="n">
-        <v>43.87328</v>
+        <v>43.75453</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05221</v>
+        <v>0.05201</v>
       </c>
       <c r="H4" t="n">
-        <v>1.87124</v>
+        <v>1.83386</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.02268</v>
+        <v>17.07925</v>
       </c>
       <c r="D6" t="n">
-        <v>16.29187</v>
+        <v>16.63743</v>
       </c>
       <c r="E6" t="n">
-        <v>16.98312</v>
+        <v>17.07158</v>
       </c>
       <c r="F6" t="n">
-        <v>22.30538</v>
+        <v>22.4742</v>
       </c>
       <c r="G6" t="n">
-        <v>35.41544</v>
+        <v>35.45585</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.1628</v>
+        <v>17.81329</v>
       </c>
       <c r="D7" t="n">
-        <v>16.53346</v>
+        <v>16.78697</v>
       </c>
       <c r="E7" t="n">
-        <v>16.81352</v>
+        <v>16.83358</v>
       </c>
       <c r="F7" t="n">
-        <v>22.29479</v>
+        <v>22.47806</v>
       </c>
       <c r="G7" t="n">
-        <v>35.62723</v>
+        <v>34.72058</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.50058</v>
+        <v>17.32246</v>
       </c>
       <c r="D8" t="n">
-        <v>16.55421</v>
+        <v>16.5025</v>
       </c>
       <c r="E8" t="n">
-        <v>17.03477</v>
+        <v>17.13402</v>
       </c>
       <c r="F8" t="n">
-        <v>21.62725</v>
+        <v>22.18642</v>
       </c>
       <c r="G8" t="n">
-        <v>34.86101</v>
+        <v>35.27382</v>
       </c>
     </row>
   </sheetData>
